--- a/tests/fixtures/expected/Test_Range_Merged.xlsx
+++ b/tests/fixtures/expected/Test_Range_Merged.xlsx
@@ -412,9 +412,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="4">
     <numFmt numFmtId="178" formatCode="#\ ##0"/>
-    <numFmt numFmtId="177" formatCode="#\ ##0.0000"/>
     <numFmt numFmtId="176" formatCode="#\ ##0.00"/>
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="177" formatCode="#\ ##0.0000"/>
   </numFmts>
   <fonts count="11" x14ac:knownFonts="1">
     <font>
